--- a/lab2/out/lab2_recalculated.xlsx
+++ b/lab2/out/lab2_recalculated.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="389">
   <si>
     <t xml:space="preserve">Ім'я</t>
   </si>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">5.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Feature complete: системне і навантажувальне тестування</t>
+    <t xml:space="preserve">Системне і навантажувальне тестування</t>
   </si>
   <si>
     <t xml:space="preserve">4.2, 4.4</t>
@@ -705,6 +705,9 @@
   </si>
   <si>
     <t xml:space="preserve">агрегування 86 400 точок до 2 с може вимагати попередньо обчислених агрегатів</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P = 16: повторний прогін навантажувального тесту k6 після оптимізації агрегатів F9 і повторна перевірка критеріїв F1...F11 після виправлень</t>
   </si>
   <si>
     <t xml:space="preserve">кількість дефектів після інтеграції з реальними лічильниками невідома до 5.2</t>
@@ -4402,11 +4405,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="60"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>72</v>
       </c>
@@ -4594,7 +4597,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>181</v>
       </c>
@@ -4629,7 +4632,9 @@
         <f aca="false">'WBS і CPM'!W17</f>
         <v>так</v>
       </c>
-      <c r="J6" s="2"/>
+      <c r="J6" s="2" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -4667,7 +4672,7 @@
         <v>так</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4686,7 +4691,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">SUMIF('WBS і CPM'!$W$2:$W$21,"так",'WBS і CPM'!$N$2:$N$21)</f>
@@ -4696,25 +4701,25 @@
         <v>46</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B11" s="7" t="n">
         <f aca="false">SUMIF('WBS і CPM'!$W$2:$W$21,"так",'WBS і CPM'!$P$2:$P$21)</f>
         <v>32.3888888888889</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B12" s="7" t="n">
         <f aca="false">SQRT(B11)</f>
@@ -4724,12 +4729,12 @@
         <v>46</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B13" s="7" t="n">
         <f aca="false">B10</f>
@@ -4739,12 +4744,12 @@
         <v>46</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B14" s="7" t="n">
         <f aca="false">B10+p2_z80*B12</f>
@@ -4754,12 +4759,12 @@
         <v>46</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B15" s="7" t="n">
         <f aca="false">B14-B13</f>
@@ -4769,12 +4774,12 @@
         <v>46</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B16" s="7" t="n">
         <f aca="false">proj_end</f>
@@ -4784,12 +4789,12 @@
         <v>46</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B17" s="7" t="n">
         <f aca="false">p2_mc_p80</f>
@@ -4799,12 +4804,12 @@
         <v>46</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B18" s="7" t="n">
         <f aca="false">ROUNDUP(MAX(B14,B17),0)</f>
@@ -4814,12 +4819,12 @@
         <v>46</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B19" s="7" t="n">
         <f aca="false">B18-B13</f>
@@ -4829,7 +4834,7 @@
         <v>46</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4844,12 +4849,12 @@
         <v>46</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B21" s="18" t="n">
         <f aca="false">p2_start</f>
@@ -4862,7 +4867,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B22" s="18" t="n">
         <f aca="false">WORKDAY(p2_start,ROUNDUP(B13,0)-1,p2_holidays)</f>
@@ -4875,7 +4880,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B23" s="18" t="n">
         <f aca="false">WORKDAY(p2_start,B18-1,p2_holidays)</f>
@@ -4885,12 +4890,12 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B24" s="18" t="n">
         <f aca="false">WORKDAY(p2_start,B18+B20-1,p2_holidays)</f>
@@ -4900,12 +4905,12 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B25" s="7" t="n">
         <f aca="false">B18/p2_days_week</f>
@@ -4947,21 +4952,21 @@
         <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>146</v>
@@ -4973,15 +4978,15 @@
         <v>145</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>13</v>
@@ -4990,12 +4995,12 @@
         <v>148</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>96</v>
@@ -5007,12 +5012,12 @@
         <v>154</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>152</v>
@@ -5024,12 +5029,12 @@
         <v>151</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>92</v>
@@ -5041,12 +5046,12 @@
         <v>158</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>100</v>
@@ -5058,12 +5063,12 @@
         <v>160</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>163</v>
@@ -5075,12 +5080,12 @@
         <v>162</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>166</v>
@@ -5092,12 +5097,12 @@
         <v>165</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>169</v>
@@ -5109,15 +5114,15 @@
         <v>168</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>8</v>
@@ -5126,12 +5131,12 @@
         <v>171</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>175</v>
@@ -5143,15 +5148,15 @@
         <v>174</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>3</v>
@@ -5160,7 +5165,7 @@
         <v>181</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5180,10 +5185,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5236,24 +5241,24 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>274</v>
-      </c>
       <c r="C24" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B25" s="6" t="n">
         <f aca="false">MAX(B17:B22)</f>
@@ -5274,7 +5279,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B26" s="6" t="n">
         <f aca="false">MEDIAN(B17:B22)</f>
@@ -5295,7 +5300,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B27" s="6" t="n">
         <f aca="false">MIN(B17:B22)</f>
@@ -5316,24 +5321,24 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B30" s="7" t="n">
         <f aca="false">'WBS і CPM'!S3</f>
@@ -5354,7 +5359,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B31" s="7" t="n">
         <f aca="false">'WBS і CPM'!S3</f>
@@ -5375,7 +5380,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B32" s="7" t="n">
         <f aca="false">'WBS і CPM'!S3</f>
@@ -5421,27 +5426,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D2" s="6" t="n">
         <f aca="false">IF(B2="S",1,IF(B2="A",2,3))</f>
@@ -5450,13 +5455,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>296</v>
       </c>
       <c r="D3" s="6" t="n">
         <f aca="false">IF(B3="S",1,IF(B3="A",2,3))</f>
@@ -5465,13 +5470,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D4" s="6" t="n">
         <f aca="false">IF(B4="S",1,IF(B4="A",2,3))</f>
@@ -5480,13 +5485,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D5" s="6" t="n">
         <f aca="false">IF(B5="S",1,IF(B5="A",2,3))</f>
@@ -5495,13 +5500,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D6" s="6" t="n">
         <f aca="false">IF(B6="S",1,IF(B6="A",2,3))</f>
@@ -5510,13 +5515,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="D7" s="6" t="n">
         <f aca="false">IF(B7="S",1,IF(B7="A",2,3))</f>
@@ -5525,30 +5530,30 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B10" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D10" s="6" t="str">
         <f aca="false">IF(B10&lt;=3,"S",IF(B10&lt;=7,"A","C"))</f>
@@ -5561,13 +5566,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B11" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D11" s="6" t="str">
         <f aca="false">IF(B11&lt;=3,"S",IF(B11&lt;=7,"A","C"))</f>
@@ -5580,13 +5585,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B12" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D12" s="6" t="str">
         <f aca="false">IF(B12&lt;=3,"S",IF(B12&lt;=7,"A","C"))</f>
@@ -5599,13 +5604,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B13" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D13" s="6" t="str">
         <f aca="false">IF(B13&lt;=3,"S",IF(B13&lt;=7,"A","C"))</f>
@@ -5618,13 +5623,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B14" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D14" s="6" t="str">
         <f aca="false">IF(B14&lt;=3,"S",IF(B14&lt;=7,"A","C"))</f>
@@ -5637,13 +5642,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B15" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D15" s="6" t="str">
         <f aca="false">IF(B15&lt;=3,"S",IF(B15&lt;=7,"A","C"))</f>
@@ -5656,13 +5661,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B16" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D16" s="6" t="str">
         <f aca="false">IF(B16&lt;=3,"S",IF(B16&lt;=7,"A","C"))</f>
@@ -5675,13 +5680,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B17" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D17" s="6" t="str">
         <f aca="false">IF(B17&lt;=3,"S",IF(B17&lt;=7,"A","C"))</f>
@@ -5694,13 +5699,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B18" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D18" s="6" t="str">
         <f aca="false">IF(B18&lt;=3,"S",IF(B18&lt;=7,"A","C"))</f>
@@ -5713,13 +5718,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B19" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D19" s="6" t="str">
         <f aca="false">IF(B19&lt;=3,"S",IF(B19&lt;=7,"A","C"))</f>
@@ -5732,13 +5737,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B20" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D20" s="6" t="str">
         <f aca="false">IF(B20&lt;=3,"S",IF(B20&lt;=7,"A","C"))</f>
@@ -5751,13 +5756,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B21" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D21" s="6" t="str">
         <f aca="false">IF(B21&lt;=3,"S",IF(B21&lt;=7,"A","C"))</f>
@@ -5770,13 +5775,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B22" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D22" s="6" t="str">
         <f aca="false">IF(B22&lt;=3,"S",IF(B22&lt;=7,"A","C"))</f>
@@ -5789,13 +5794,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B23" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D23" s="6" t="str">
         <f aca="false">IF(B23&lt;=3,"S",IF(B23&lt;=7,"A","C"))</f>
@@ -5808,13 +5813,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B24" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D24" s="6" t="str">
         <f aca="false">IF(B24&lt;=3,"S",IF(B24&lt;=7,"A","C"))</f>
@@ -5827,21 +5832,21 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B27" s="6" t="n">
         <f aca="false">COUNTIF(B2:B7,"S")</f>
@@ -5857,7 +5862,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B28" s="6" t="n">
         <f aca="false">COUNTIF(B2:B7,"A")</f>
@@ -5873,7 +5878,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B29" s="6" t="n">
         <f aca="false">COUNTIF(B2:B7,"C")</f>
@@ -5889,7 +5894,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -5900,7 +5905,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B31" s="6" t="n">
         <f aca="false">COUNTIF(D10:D24,"S")</f>
@@ -5916,7 +5921,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B32" s="6" t="n">
         <f aca="false">COUNTIF(D10:D24,"A")</f>
@@ -5932,7 +5937,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B33" s="6" t="n">
         <f aca="false">COUNTIF(D10:D24,"C")</f>
@@ -5948,7 +5953,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -5959,7 +5964,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -5970,7 +5975,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B36" s="6" t="n">
         <f aca="false">p2_tcf</f>
@@ -5987,7 +5992,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -5998,7 +6003,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B38" s="6" t="n">
         <f aca="false">p2_pf</f>
@@ -6012,7 +6017,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -6023,7 +6028,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -6034,7 +6039,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -6048,19 +6053,19 @@
         <v>56</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6190,7 +6195,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B49" s="19" t="n">
         <f aca="false">B45+B46</f>
@@ -6215,7 +6220,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B50" s="20"/>
       <c r="C50" s="8" t="n">
@@ -6237,7 +6242,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B51" s="20"/>
       <c r="C51" s="21"/>
@@ -6256,7 +6261,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B52" s="20"/>
       <c r="C52" s="21"/>
@@ -6311,13 +6316,13 @@
         <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6442,7 +6447,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">SUM(B2:B6)</f>
@@ -6467,18 +6472,18 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B10" s="7" t="n">
         <f aca="false">MAX('WBS і CPM'!S2)</f>
@@ -6491,7 +6496,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B11" s="7" t="n">
         <f aca="false">MAX('WBS і CPM'!S3)</f>
@@ -6504,7 +6509,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B12" s="7" t="n">
         <f aca="false">MAX('WBS і CPM'!S5,'WBS і CPM'!S6,'WBS і CPM'!S7,'WBS і CPM'!S8,'WBS і CPM'!S9,'WBS і CPM'!S10,'WBS і CPM'!S11,'WBS і CPM'!S12,'WBS і CPM'!S13,'WBS і CPM'!S14,'WBS і CPM'!S15)</f>
@@ -6517,7 +6522,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B13" s="7" t="n">
         <f aca="false">MAX('WBS і CPM'!S18)</f>
@@ -6530,7 +6535,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B14" s="7" t="n">
         <f aca="false">MAX('WBS і CPM'!S21)</f>
@@ -6543,7 +6548,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B15" s="7" t="n">
         <f aca="false">bl_days</f>
@@ -6556,7 +6561,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B16" s="6" t="n">
         <f aca="false">bl_days+p2_mr</f>
@@ -6593,27 +6598,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B2" s="6" t="str">
         <f aca="false">COUNTA('WBS і CPM'!A2:A21)&amp;" пакетів"</f>
@@ -6638,14 +6643,14 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B3" s="6" t="str">
         <f aca="false">'Backlog і velocity'!C14&amp;" SP"</f>
         <v>116 SP</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D3" s="8" t="n">
         <f aca="false">'Backlog і velocity'!E30</f>
@@ -6662,7 +6667,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B4" s="6" t="str">
         <f aca="false">TEXT(ucp_val,"0.00")&amp;" UCP"</f>

--- a/lab2/out/lab2_recalculated.xlsx
+++ b/lab2/out/lab2_recalculated.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">П</t>
   </si>
   <si>
-    <t xml:space="preserve">після тестів A1, A2, A5 з ЛР № 1</t>
+    <t xml:space="preserve">після тестів A1, A2 і часткової перевірки A5 з ЛР № 1</t>
   </si>
   <si>
     <t xml:space="preserve">p2_hours</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">Пояснення P</t>
   </si>
   <si>
-    <t xml:space="preserve">ключова невизначеність варіанта: карта регістрів Modbus надходить від постачальника лічильників (A12), частина лічильників відповідає нестабільно; у P закладено 2 ітерації очікування по 5 робочих днів</t>
+    <t xml:space="preserve">ключова невизначеність варіанта: карта регістрів Modbus надходить від постачальника лічильників (A12), частина лічильників відповідає нестабільно; у P закладено 2 ітерації очікування по 5 робочих днів і 2 дні повторного тесту зчитування</t>
   </si>
   <si>
     <t xml:space="preserve">ключова невизначеність варіанта на рівні пакета: поведінка конкретних лічильників після перезапуску (скидання лічильника, перехід через нуль), ідемпотентність дозавантаження</t>
   </si>
   <si>
-    <t xml:space="preserve">поріг max(3σ; 10%) може потребувати 2...3 циклів налаштування на розмічених даних (A7)</t>
+    <t xml:space="preserve">поріг max(3σ; 10%) може потребувати 3 додаткових циклів налаштування на розмічених даних (A7)</t>
   </si>
   <si>
     <t xml:space="preserve">агрегування 86 400 точок до 2 с може вимагати попередньо обчислених агрегатів</t>
@@ -4441,7 +4441,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>139</v>
       </c>
